--- a/Phytium_PPE_System_SourceCode/功能需求表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能需求表.xlsx
@@ -1162,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="16.5583333333333" customWidth="1" style="13" min="1" max="1"/>
@@ -1498,56 +1498,83 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>REQ-12</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>双核通信与安全监湧</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>主从核心跳监控与安全接管</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>主核定时（500ms）向从核发送心跳报文。若从核连续4次（2秒）未收到心跳，则判定主核失效，主动接管硬件外设，并进入安全状态（触发蜂鸣器长鸣报警）。</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>已实现</t>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>安全可靠性保障模块</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>主从核心跳通信</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>在 Linux 主核与 Bare-metal 从核间建立基于 OpenAMP RPMsg 的双向异步心跳通信，主核由独立 heartbeat_task 线程每 500ms 下发 DEVICE_CORE_CHECK 校验帧，从核实时监控主核业务存活状态以解决 SGI 邮箱中断丢失引起的僵死问题。</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>已实现 (Active Heartbeat心跳线程真机测试通过)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>REQ-13</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>安全管控与容错模块</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>看门狗(WDT)故障恢复与告警</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>在主核心跳中断或主控程序跑飞时，从核定期复位飞腾派硬件看门狗。若主从核均死机，看门狗超时溢叺将触发处理器硬件重启，确保系统可靠性。</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>已实现</t>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>安全可靠性保障模块</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>看门狗(WDT)容错与自愈</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>在主核系统配置飞腾底层 FWDT 硬件看门狗，当主核宕机心跳超时（连续 4 次超时，共 2s）后，从核自动接管底层外设，进入 Fail-Safe 安全降级状态驱动蜂鸣器长鸣并停止喂狗，在 10s WDT 超时后触发处理器硬件冷重启实现全面自愈。</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>已实现 (硬件看门狗超时10s冷重启真机测试通过)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>REQ-14</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>智能安全顾问模块</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek AI 安全整改建议</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>接入真实的 DeepSeek LLM API，在检测到违规事件时异步调用生成智能化的现场安全整改建议，规避表情符防止 UI 界面方框乱码，并对违规次数进行滑动聚合展示。</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>已实现 (DeepSeek API 接入及乱码规避真机测试通过)</t>
         </is>
       </c>
     </row>

--- a/Phytium_PPE_System_SourceCode/功能需求表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能需求表.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -243,6 +243,15 @@
       <color theme="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="36">
     <fill>
@@ -456,7 +465,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -586,6 +595,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
@@ -736,7 +751,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -777,6 +792,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1174,405 +1198,405 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.25" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>需求编号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>模块名称</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>需求名称</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>功能需求描述</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>功能实现情况</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>REQ-01</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>视频流采集模块</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>USB摄像头实时拉流</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>通过 V4L2 驱动阻塞式拉取视频流，物理隔离在 Core 0 运行，保障 AI 算力。</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>已实现 (帧率稳定)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15" customFormat="1" customHeight="1" s="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>REQ-02</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>视频流采集模块</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>视频源无感热切换</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>支持摄像头监控与本地视频分析动态热切换，具备自动回退机制。</t>
-        </is>
-      </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>支持摄像头监控与本地视频 analysis 动态热切换，具备自动回退机制。</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>已实现 (无缝切换)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="15" customFormat="1" customHeight="1" s="2">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>REQ-03</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>数据总线模块</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>多线程无锁数据传输</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>采用 SPSC 无锁环形队列进行数据分发，基于 alignas(64) 消除伪共享。</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>已实现 (纯用户态流转)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="15" customFormat="1" customHeight="1" s="3">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>REQ-04</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>AI视觉推理模块</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>PPE 八类目标检测</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>依托 NCNN 引擎与 QAT INT8 量化模型，实现高保真 PPE 实时检测。</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>已实现 (mAP@0.5达80%)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customFormat="1" customHeight="1" s="2">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>REQ-05</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>AI视觉推理模块</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>复杂遮挡目标追踪</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>结合卡尔曼滤波与 ByteTrack 二次关联，维持极端遮挡工况下的 ID 稳定。</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>已实现 (抗遮挡性强)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customFormat="1" customHeight="1" s="3">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>REQ-06</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>软硬联动模块</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>违规报警物理阻断</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>通过 OpenAMP RPMsg 协议驱动从核蜂鸣器，响应延迟达微秒级。</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>已实现 (异构联动成功)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>REQ-07</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>软硬联动模块</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>灾害环境硬中断报警</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>从核监控火焰及气体传感器，支持最高优先级硬件中断报警推送。</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>火焰传感器实现，气体传感器待验证</t>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>从核监控火焰及烟雾传感器，支持最高优先级硬件中断报警推送。</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>已实现 (火焰及烟雾传感器真机测试通过)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customFormat="1" customHeight="1" s="3">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>REQ-08</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>UI交互渲染模块</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>零拷贝监控大屏</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>基于 Qt5 实现零拷贝图像渲染，动态叠加 OSD 报警框及置信度。</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>已实现 (渲染低延迟)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customFormat="1" customHeight="1" s="2">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>REQ-09</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>UI交互渲染模块</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>硬件状态自视看板</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>解析 /proc/stat 动态展示 CPU 真实负载及核心热敏温度。</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>已实现 (数据动态刷新)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customFormat="1" customHeight="1" s="3">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>REQ-10</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>本地存储模块</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>违规异步抓拍落盘</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>专职 I/O 线程后台执行 JPEG 编码与 CSV 记录，确保断电证据不丢失。</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>已实现 (IO 剥离成功)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customFormat="1" customHeight="1" s="2">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>REQ-11</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>本地存储模块</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>磁盘防洪自清洁机制</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>当磁盘占用超 85% 时自动启动循环覆盖，确保系统长期无人值守运行。</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>已实现 (自闭环运行)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>REQ-12</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>安全可靠性保障模块</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>主从核心跳通信</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>在 Linux 主核与 Bare-metal 从核间建立基于 OpenAMP RPMsg 的双向异步心跳通信，主核由独立 heartbeat_task 线程每 500ms 下发 DEVICE_CORE_CHECK 校验帧，从核实时监控主核业务存活状态以解决 SGI 邮箱中断丢失引起的僵死问题。</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>已实现 (Active Heartbeat心跳线程真机测试通过)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>REQ-13</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>安全可靠性保障模块</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>看门狗(WDT)容错与自愈</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>在主核系统配置飞腾底层 FWDT 硬件看门狗，当主核宕机心跳超时（连续 4 次超时，共 2s）后，从核自动接管底层外设，进入 Fail-Safe 安全降级状态驱动蜂鸣器长鸣并停止喂狗，在 10s WDT 超时后触发处理器硬件冷重启实现全面自愈。</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>在主核系统配置飞腾底层 FWDT 硬件看门狗，当主核宕机心跳超时（连续 4 次超时，共 2s）后，从核自动接管底层外设，进入 Fail-Safe 安全降级状态驱动蜂鸣器长鸣并停止喂狗，在 10s WDT 超时后触发处理器硬件 cold reset 冷重启实现全面自愈。</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>已实现 (硬件看门狗超时10s冷重启真机测试通过)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>REQ-14</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>智能安全顾问模块</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>DeepSeek AI 安全整改建议</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>接入真实的 DeepSeek LLM API，在检测到违规事件时异步调用生成智能化的现场安全整改建议，规避表情符防止 UI 界面方框乱码，并对违规次数进行滑动聚合展示。</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>已实现 (DeepSeek API 接入及乱码规避真机测试通过)</t>
         </is>

--- a/Phytium_PPE_System_SourceCode/功能需求表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能需求表.xlsx
@@ -1189,15 +1189,15 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="16.5583333333333" customWidth="1" style="13" min="1" max="1"/>
-    <col width="26.1083333333333" customWidth="1" style="13" min="2" max="2"/>
-    <col width="33.3333333333333" customWidth="1" style="13" min="3" max="3"/>
-    <col width="69.8833333333333" customWidth="1" style="13" min="4" max="4"/>
-    <col width="26.1083333333333" customWidth="1" style="13" min="5" max="5"/>
+    <col width="12" customWidth="1" style="13" min="1" max="1"/>
+    <col width="20" customWidth="1" style="13" min="2" max="2"/>
+    <col width="20" customWidth="1" style="13" min="3" max="3"/>
+    <col width="55" customWidth="1" style="13" min="4" max="4"/>
+    <col width="25" customWidth="1" style="13" min="5" max="5"/>
     <col width="40.1083333333333" customWidth="1" style="13" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.25" customFormat="1" customHeight="1" s="1">
+    <row r="1" ht="29" customFormat="1" customHeight="1" s="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
           <t>需求编号</t>
@@ -1224,7 +1224,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customFormat="1" customHeight="1" s="2">
+    <row r="2" ht="29" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>REQ-01</t>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customFormat="1" customHeight="1" s="3">
+    <row r="3" ht="29" customFormat="1" customHeight="1" s="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
           <t>REQ-02</t>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customFormat="1" customHeight="1" s="2">
+    <row r="4" ht="29" customFormat="1" customHeight="1" s="2">
       <c r="A4" s="15" t="inlineStr">
         <is>
           <t>REQ-03</t>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customFormat="1" customHeight="1" s="3">
+    <row r="5" ht="29" customFormat="1" customHeight="1" s="3">
       <c r="A5" s="15" t="inlineStr">
         <is>
           <t>REQ-04</t>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customFormat="1" customHeight="1" s="2">
+    <row r="6" ht="29" customFormat="1" customHeight="1" s="2">
       <c r="A6" s="15" t="inlineStr">
         <is>
           <t>REQ-05</t>
@@ -1359,7 +1359,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customFormat="1" customHeight="1" s="3">
+    <row r="7" ht="29" customFormat="1" customHeight="1" s="3">
       <c r="A7" s="15" t="inlineStr">
         <is>
           <t>REQ-06</t>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customFormat="1" customHeight="1" s="2">
+    <row r="8" ht="29" customFormat="1" customHeight="1" s="2">
       <c r="A8" s="15" t="inlineStr">
         <is>
           <t>REQ-07</t>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customFormat="1" customHeight="1" s="3">
+    <row r="9" ht="29" customFormat="1" customHeight="1" s="3">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>REQ-08</t>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customFormat="1" customHeight="1" s="2">
+    <row r="10" ht="29" customFormat="1" customHeight="1" s="2">
       <c r="A10" s="15" t="inlineStr">
         <is>
           <t>REQ-09</t>
@@ -1467,7 +1467,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customFormat="1" customHeight="1" s="3">
+    <row r="11" ht="29" customFormat="1" customHeight="1" s="3">
       <c r="A11" s="15" t="inlineStr">
         <is>
           <t>REQ-10</t>
@@ -1494,7 +1494,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customFormat="1" customHeight="1" s="2">
+    <row r="12" ht="29" customFormat="1" customHeight="1" s="2">
       <c r="A12" s="15" t="inlineStr">
         <is>
           <t>REQ-11</t>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>当磁盘占用超 85% 时自动启动循环覆盖，确保系统长期无人值守运行。</t>
+          <t>当磁盘占用超 85% 时自动启动循环覆盖，确保 system 长期无人值守运行。</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="63" customHeight="1" s="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
           <t>REQ-12</t>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="63" customHeight="1" s="13">
       <c r="A14" s="15" t="inlineStr">
         <is>
           <t>REQ-13</t>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="46" customHeight="1" s="13">
       <c r="A15" s="15" t="inlineStr">
         <is>
           <t>REQ-14</t>

--- a/Phytium_PPE_System_SourceCode/功能需求表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能需求表.xlsx
@@ -1386,7 +1386,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="29" customFormat="1" customHeight="1" s="2">
+    <row r="8" ht="46" customFormat="1" customHeight="1" s="2">
       <c r="A8" s="15" t="inlineStr">
         <is>
           <t>REQ-07</t>
@@ -1399,17 +1399,17 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>灾害环境硬中断报警</t>
+          <t>灾害环境硬中断与环境监测</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>从核监控火焰及烟雾传感器，支持最高优先级硬件中断报警推送。</t>
+          <t>从核实时监控火焰、有害气体（烟雾）及温湿度环境传感器，支持最高优先级硬件中断报警推送与高频数据采集。</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>已实现 (火焰及烟雾传感器真机测试通过)</t>
+          <t>已实现 (火焰、有害气体及温湿度传感器真机测试通过)</t>
         </is>
       </c>
     </row>

--- a/Phytium_PPE_System_SourceCode/功能需求表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能需求表.xlsx
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>在主核系统配置飞腾底层 FWDT 硬件看门狗，当主核宕机心跳超时（连续 4 次超时，共 2s）后，从核自动接管底层外设，进入 Fail-Safe 安全降级状态驱动蜂鸣器长鸣并停止喂狗，在 10s WDT 超时后触发处理器硬件 cold reset 冷重启实现全面自愈。</t>
+          <t>在主核系统配置飞腾底层 FWDT 硬件看门狗，当主核宕机心跳超时（连续 4 次超时，共 2s）后，从核自动接管底层外设，进入 Fail-Safe 安全降级状态停止喂狗，在 10s WDT 超时后触发处理器硬件 cold reset 冷重启实现全面自愈。</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">

--- a/Phytium_PPE_System_SourceCode/功能需求表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能需求表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="新建 Text Document" sheetId="1" r:id="rId1"/>
@@ -215,7 +215,7 @@
     <t>看门狗(WDT)容错与自愈</t>
   </si>
   <si>
-    <t>在主核系统配置飞腾底层 FWDT 硬件看门狗，当主核宕机心跳超时（连续 4 次超时，共 2s）后，从核自动接管底层外设，进入 Fail-Safe 安全降级状态停止喂狗，在 10s WDT 超时后触发处理器硬件 cold reset 冷重启实现全面自愈。</t>
+    <t>在主核系统配置飞腾底层 FWDT 硬件看门狗，当主核宕机心跳超时（连续10次超时，共 5s）后，从核自动接管底层外设，进入 Fail-Safe 安全降级状态停止喂狗，在 1s WDT 超时后触发处理器硬件 cold reset 冷重启实现全面自愈。</t>
   </si>
   <si>
     <t>已实现 (硬件看门狗超时10s冷重启真机测试通过)</t>

--- a/Phytium_PPE_System_SourceCode/功能需求表.xlsx
+++ b/Phytium_PPE_System_SourceCode/功能需求表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="27950" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="新建 Text Document" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
     <t>PPE 八类目标检测</t>
   </si>
   <si>
-    <t>依托 NCNN 引擎与 QAT INT8 量化模型，实现高保真 PPE 实时检测。</t>
+    <t>依托 NCNN 引擎与 INT8 量化模型，实现高保真 PPE 实时检测。</t>
   </si>
   <si>
     <t>已实现 (mAP@0.5达80%)</t>
